--- a/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
+++ b/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
@@ -1,33 +1,14 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +19,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +27,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,96 +390,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Site</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>URhIn.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Site</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>URhIn.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.983</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
+++ b/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
@@ -1,14 +1,37 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga1B" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co2A-Ga1B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co1A-Co2A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co1A-Ga2B" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga1B-Ga2B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co1A" sheetId="6" state="visible" r:id="rId6"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -390,4 +422,280 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
+++ b/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga1B" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co2A-Ga1B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co1A-Co2A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co1A-Ga2B" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga1B-Ga2B" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co1A" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru1-Ge1 (2)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge1-Ge1 (3)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La1-Ge1 (1)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir1-Ge1 (1)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu1-Ge1 (1)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce1-Ge1 (1)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,15 +453,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.543</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.554</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -476,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,15 +518,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.501</v>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.383</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -545,15 +600,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.501</v>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.241</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -591,15 +648,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.501</v>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.537</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -637,15 +696,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.501</v>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.182</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -683,15 +744,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.227</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>

--- a/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
+++ b/20240307_mendeleev_test/output/20240307_mendeleev_test_pairs.xlsx
@@ -1,14 +1,135 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Rh2-Si" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rh1-Rh1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ru1-Ge1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ge1-Ge1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La1-Ge1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pt1-Sb2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="La-Pt1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sb2-Sb2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Pt1-Pt1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="La-Sb2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Si1A-Si2A" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fe1B-Si2A" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Y1-Si2A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Fe2B-Si1A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Fe1B-Fe2B" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Y1-Fe2B" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Rh1-Ge1" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Dy1-Ge1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Si,Ni1-Si,Ni2" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Si,Ni2-Si,Ni2" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pr-Si,Ni2" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Pr-Si,Ni1" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Si,Ni1-Si,Ni1" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Ga1-Ga1A" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ga1-Ga2A" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Ni2B-Ga1" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Ni2B-Ga1A" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Ni1B-Ga1" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Ce1-Ni1B" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Ce1-Ga1A" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Ga1A-Ga2A" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Ni1B-Ga2A" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Ce1-Ga1" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Ni1B-Ni2B" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Ga1-Ga1" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Ce1B-Pd1" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Ce1-Pd1" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Pd1-In1A" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Pd1-Pd1" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Yb1-Ge1" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Co1-Ge2" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Fe1-Ga2" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Dy3-Dy3" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Dy3-Fe1" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Fe1-Fe1" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Dy3-Ga2" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Ga2-Ga2" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Si1,Pd1B-Si1,Pd1B" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Si1,Pd1A-Si1,Pd1B" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Lu1-Si1,Pd1A" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="Si1,Pd1A-Si1,Pd1A" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Lu1-Si1,Pd1B" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Er5-Er7" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Er6-Co1" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Er3-Co1" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Er2-Er4" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="Er3-Er5" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="Er3-In2" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="In1-In1" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="In1-In2" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="Er1-Er6" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="Er1-Co1" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="Er4-Co1" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="Er4-In1" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="Er2-In2" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="Er5-In1" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="Er7-In1" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="Er2-Er2" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="Er3-In1" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="Fe1A-Si1" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="Si1-Si1B" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="Lu1-Ge1" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="Fe1-Ge" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="Ge-Ge2" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="Fe-Fe" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="Gd1-Ge1" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="Er1-Ge1" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="Ni1-Sb2" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="Ni1-Ni1" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="Tb1-Ge1" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="Ho1-Ge1" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="Er-Ni" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="Ni-Ni" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet name="Ni-In1,Er1B" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet name="Ni-In2,Er2A" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet name="Ni-In2,Er2B" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet name="Ni-In1,Er1A" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet name="Sm1-Ge1" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet name="Nd1-Ge1" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet name="Si1-Si1" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet name="Ni2-Ni2" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet name="Ni2-Si1" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet name="Gd-Si1" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet name="Gd-Ni2" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet name="Ni1A-Si1" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet name="Eu1-Si1" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet name="Pr1-Ge1" sheetId="97" state="visible" r:id="rId97"/>
+    <sheet name="Fe2-Si1" sheetId="98" state="visible" r:id="rId98"/>
+    <sheet name="Fe2-Fe2" sheetId="99" state="visible" r:id="rId99"/>
+    <sheet name="Ce-Si1" sheetId="100" state="visible" r:id="rId100"/>
+    <sheet name="Ce-Fe2" sheetId="101" state="visible" r:id="rId101"/>
+    <sheet name="Ir1-Ge1" sheetId="102" state="visible" r:id="rId102"/>
+    <sheet name="Eu1-Ge1" sheetId="103" state="visible" r:id="rId103"/>
+    <sheet name="Ce1-Ge1" sheetId="104" state="visible" r:id="rId104"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,12 +148,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -390,4 +520,5328 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>527000.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301182.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>527000.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.513</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.166</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.166</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.431</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301188.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301180.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301185.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301183.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.443</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301188.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301182.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.447</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.436</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5.078</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.493</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.571</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.376</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1617211.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1617211.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301180.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301183.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301185.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.141</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>